--- a/outputs_xlsx_solution/test_new4.4-wide-NB-1.xlsx
+++ b/outputs_xlsx_solution/test_new4.4-wide-NB-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fadd F2, F2, F3</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -663,7 +669,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -683,16 +689,16 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -712,16 +718,19 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -741,22 +750,28 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +794,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -802,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -814,22 +829,22 @@
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -849,7 +864,10 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
@@ -861,22 +879,22 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -896,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -911,37 +929,37 @@
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -952,7 +970,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -961,7 +979,7 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V10" t="s">
         <v>14</v>
@@ -973,7 +991,7 @@
         <v>14</v>
       </c>
       <c r="Y10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -984,7 +1002,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -993,16 +1011,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
         <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1022,16 +1040,16 @@
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N12" t="s">
         <v>14</v>
       </c>
       <c r="O12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1042,7 +1060,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1051,19 +1069,19 @@
         <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
       </c>
       <c r="K13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1074,7 +1092,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1083,19 +1101,19 @@
         <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
         <v>14</v>
       </c>
       <c r="L14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1106,7 +1124,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1115,16 +1133,16 @@
         <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
         <v>14</v>
       </c>
       <c r="M15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1144,7 +1162,25 @@
         <v>9</v>
       </c>
       <c r="O16" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>15</v>
+      </c>
+      <c r="R16" t="s">
+        <v>15</v>
+      </c>
+      <c r="S16" t="s">
+        <v>15</v>
+      </c>
+      <c r="T16" t="s">
+        <v>15</v>
+      </c>
+      <c r="U16" t="s">
+        <v>15</v>
       </c>
       <c r="V16" t="s">
         <v>14</v>
@@ -1159,7 +1195,7 @@
         <v>14</v>
       </c>
       <c r="Z16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1170,7 +1206,7 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M17" t="s">
         <v>5</v>
@@ -1179,10 +1215,10 @@
         <v>9</v>
       </c>
       <c r="O17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s">
         <v>14</v>
@@ -1194,13 +1230,13 @@
         <v>14</v>
       </c>
       <c r="AC17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1211,7 +1247,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M18" t="s">
         <v>5</v>
@@ -1220,16 +1256,16 @@
         <v>9</v>
       </c>
       <c r="P18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
         <v>14</v>
       </c>
       <c r="R18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1249,16 +1285,16 @@
         <v>9</v>
       </c>
       <c r="P19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R19" t="s">
         <v>14</v>
       </c>
       <c r="S19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1269,7 +1305,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N20" t="s">
         <v>5</v>
@@ -1278,19 +1314,22 @@
         <v>9</v>
       </c>
       <c r="P20" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>15</v>
       </c>
       <c r="R20" t="s">
         <v>14</v>
       </c>
       <c r="S20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1301,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N21" t="s">
         <v>5</v>
@@ -1310,16 +1349,16 @@
         <v>9</v>
       </c>
       <c r="Q21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T21" t="s">
         <v>14</v>
       </c>
       <c r="U21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1330,7 +1369,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
         <v>5</v>
@@ -1339,16 +1378,16 @@
         <v>9</v>
       </c>
       <c r="Q22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U22" t="s">
         <v>14</v>
       </c>
       <c r="V22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1368,22 +1407,31 @@
         <v>9</v>
       </c>
       <c r="Q23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V23" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="W23" t="s">
+        <v>15</v>
+      </c>
+      <c r="X23" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>15</v>
       </c>
       <c r="Z23" t="s">
         <v>14</v>
@@ -1398,13 +1446,13 @@
         <v>14</v>
       </c>
       <c r="AD23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1415,7 +1463,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O24" t="s">
         <v>5</v>
@@ -1424,7 +1472,7 @@
         <v>9</v>
       </c>
       <c r="V24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="s">
         <v>14</v>
@@ -1436,13 +1484,13 @@
         <v>14</v>
       </c>
       <c r="AI24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1453,7 +1501,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O25" t="s">
         <v>5</v>
@@ -1462,16 +1510,16 @@
         <v>9</v>
       </c>
       <c r="V25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W25" t="s">
         <v>14</v>
       </c>
       <c r="X25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1491,25 +1539,25 @@
         <v>9</v>
       </c>
       <c r="V26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s">
         <v>14</v>
       </c>
       <c r="AA26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1520,7 +1568,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P27" t="s">
         <v>5</v>
@@ -1529,19 +1577,19 @@
         <v>9</v>
       </c>
       <c r="Y27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="s">
         <v>14</v>
       </c>
       <c r="AA27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1552,7 +1600,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P28" t="s">
         <v>5</v>
@@ -1561,16 +1609,16 @@
         <v>9</v>
       </c>
       <c r="Y28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB28" t="s">
         <v>14</v>
       </c>
       <c r="AC28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1581,7 +1629,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P29" t="s">
         <v>5</v>
@@ -1590,16 +1638,16 @@
         <v>9</v>
       </c>
       <c r="Y29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="s">
         <v>14</v>
       </c>
       <c r="AD29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1619,7 +1667,22 @@
         <v>9</v>
       </c>
       <c r="Z30" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>15</v>
       </c>
       <c r="AF30" t="s">
         <v>14</v>
@@ -1634,13 +1697,13 @@
         <v>14</v>
       </c>
       <c r="AJ30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1651,7 +1714,7 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q31" t="s">
         <v>5</v>
@@ -1660,7 +1723,7 @@
         <v>9</v>
       </c>
       <c r="Z31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s">
         <v>14</v>
@@ -1672,10 +1735,10 @@
         <v>14</v>
       </c>
       <c r="AO31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1686,7 +1749,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32" t="s">
         <v>5</v>
@@ -1695,22 +1758,22 @@
         <v>9</v>
       </c>
       <c r="Z32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="s">
         <v>14</v>
       </c>
       <c r="AB32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1730,31 +1793,31 @@
         <v>9</v>
       </c>
       <c r="Z33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="s">
         <v>14</v>
       </c>
       <c r="AG33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1765,7 +1828,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R34" t="s">
         <v>5</v>
@@ -1774,19 +1837,19 @@
         <v>9</v>
       </c>
       <c r="AE34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF34" t="s">
         <v>14</v>
       </c>
       <c r="AG34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1797,7 +1860,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R35" t="s">
         <v>5</v>
@@ -1806,16 +1869,16 @@
         <v>9</v>
       </c>
       <c r="AE35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH35" t="s">
         <v>14</v>
       </c>
       <c r="AI35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1826,7 +1889,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R36" t="s">
         <v>5</v>
@@ -1835,16 +1898,16 @@
         <v>9</v>
       </c>
       <c r="AE36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI36" t="s">
         <v>14</v>
       </c>
       <c r="AJ36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1864,7 +1927,22 @@
         <v>9</v>
       </c>
       <c r="AF37" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>15</v>
       </c>
       <c r="AL37" t="s">
         <v>14</v>
@@ -1879,10 +1957,10 @@
         <v>14</v>
       </c>
       <c r="AP37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1893,7 +1971,7 @@
         <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S38" t="s">
         <v>5</v>
@@ -1902,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="AF38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ38" t="s">
         <v>14</v>
@@ -1914,7 +1992,7 @@
         <v>14</v>
       </c>
       <c r="AT38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1925,7 +2003,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S39" t="s">
         <v>5</v>
@@ -1934,22 +2012,22 @@
         <v>9</v>
       </c>
       <c r="AF39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG39" t="s">
         <v>14</v>
       </c>
       <c r="AH39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -1969,31 +2047,31 @@
         <v>9</v>
       </c>
       <c r="AF40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s">
         <v>14</v>
       </c>
       <c r="AM40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -2004,7 +2082,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T41" t="s">
         <v>5</v>
@@ -2013,19 +2091,19 @@
         <v>9</v>
       </c>
       <c r="AK41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL41" t="s">
         <v>14</v>
       </c>
       <c r="AM41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -2036,7 +2114,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V42" t="s">
         <v>5</v>
@@ -2045,16 +2123,16 @@
         <v>9</v>
       </c>
       <c r="AK42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN42" t="s">
         <v>14</v>
       </c>
       <c r="AO42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -2065,7 +2143,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y43" t="s">
         <v>5</v>
@@ -2074,16 +2152,16 @@
         <v>9</v>
       </c>
       <c r="AK43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO43" t="s">
         <v>14</v>
       </c>
       <c r="AP43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -2094,7 +2172,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP44" t="s">
         <v>5</v>
@@ -2103,18 +2181,18 @@
         <v>9</v>
       </c>
       <c r="AR44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT44" t="s">
         <v>14</v>
       </c>
       <c r="AU44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
@@ -2122,7 +2200,7 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
@@ -2130,15 +2208,15 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50">
@@ -2146,39 +2224,55 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
